--- a/data_lake/industry/TrendForce/NAND Flash.xlsx
+++ b/data_lake/industry/TrendForce/NAND Flash.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/industry/TrendForce/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data_lake\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{858ED5CF-332E-A648-B770-CB86AF6C10A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E5F129-A6D3-4E7D-A42D-68584D0F38E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26120" yWindow="1100" windowWidth="24840" windowHeight="23800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11430" yWindow="0" windowWidth="11700" windowHeight="14730" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="76">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -601,6 +601,9 @@
                 <c:pt idx="23">
                   <c:v>46209</c:v>
                 </c:pt>
+                <c:pt idx="24">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -681,6 +684,9 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>3.9350000000000001</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4.0380000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -799,6 +805,9 @@
                 <c:pt idx="23">
                   <c:v>46209</c:v>
                 </c:pt>
+                <c:pt idx="24">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -879,6 +888,9 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>3.6</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3.5630000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -997,6 +1009,9 @@
                 <c:pt idx="23">
                   <c:v>46209</c:v>
                 </c:pt>
+                <c:pt idx="24">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1077,6 +1092,9 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>29.681999999999999</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>31.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1195,6 +1213,9 @@
                 <c:pt idx="23">
                   <c:v>46209</c:v>
                 </c:pt>
+                <c:pt idx="24">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1275,6 +1296,9 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>14.733000000000001</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>15.438000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1645,6 +1669,9 @@
                 <c:pt idx="33">
                   <c:v>46209</c:v>
                 </c:pt>
+                <c:pt idx="34">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1755,6 +1782,9 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>19.861999999999998</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>19.292999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1903,6 +1933,9 @@
                 <c:pt idx="33">
                   <c:v>46209</c:v>
                 </c:pt>
+                <c:pt idx="34">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2012,6 +2045,9 @@
                   <c:v>10.18</c:v>
                 </c:pt>
                 <c:pt idx="33">
+                  <c:v>10.18</c:v>
+                </c:pt>
+                <c:pt idx="34">
                   <c:v>10.18</c:v>
                 </c:pt>
               </c:numCache>
@@ -2161,6 +2197,9 @@
                 <c:pt idx="33">
                   <c:v>46209</c:v>
                 </c:pt>
+                <c:pt idx="34">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2270,6 +2309,9 @@
                   <c:v>6.4870000000000001</c:v>
                 </c:pt>
                 <c:pt idx="33">
+                  <c:v>6.4870000000000001</c:v>
+                </c:pt>
+                <c:pt idx="34">
                   <c:v>6.4870000000000001</c:v>
                 </c:pt>
               </c:numCache>
@@ -2641,6 +2683,9 @@
                 <c:pt idx="33">
                   <c:v>46209</c:v>
                 </c:pt>
+                <c:pt idx="34">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2751,6 +2796,9 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>2.875</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2.9249999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2899,6 +2947,9 @@
                 <c:pt idx="33">
                   <c:v>46209</c:v>
                 </c:pt>
+                <c:pt idx="34">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3009,6 +3060,9 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>4.3499999999999996</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>4.375</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3157,6 +3211,9 @@
                 <c:pt idx="33">
                   <c:v>46209</c:v>
                 </c:pt>
+                <c:pt idx="34">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3267,6 +3324,9 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>6.65</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>6.665</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3415,6 +3475,9 @@
                 <c:pt idx="33">
                   <c:v>46209</c:v>
                 </c:pt>
+                <c:pt idx="34">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3524,6 +3587,9 @@
                   <c:v>13.4</c:v>
                 </c:pt>
                 <c:pt idx="33">
+                  <c:v>12.6</c:v>
+                </c:pt>
+                <c:pt idx="34">
                   <c:v>12.6</c:v>
                 </c:pt>
               </c:numCache>
@@ -5789,13 +5855,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:Y37"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" style="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.1640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6328125" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1796875" style="18" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="19"/>
     <col min="26" max="16384" width="9" style="15"/>
   </cols>
@@ -7725,6 +7791,56 @@
       </c>
       <c r="P36" s="19">
         <v>14.733000000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37" s="16">
+        <v>46209</v>
+      </c>
+      <c r="B37" s="16">
+        <v>46216</v>
+      </c>
+      <c r="C37" s="17">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E37" s="19">
+        <v>4.55</v>
+      </c>
+      <c r="F37" s="19">
+        <v>3.7</v>
+      </c>
+      <c r="G37" s="19">
+        <v>4.0380000000000003</v>
+      </c>
+      <c r="H37" s="19">
+        <v>3.85</v>
+      </c>
+      <c r="I37" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="J37" s="19">
+        <v>3.5630000000000002</v>
+      </c>
+      <c r="K37" s="19">
+        <v>45</v>
+      </c>
+      <c r="L37" s="19">
+        <v>27</v>
+      </c>
+      <c r="M37" s="19">
+        <v>31.1</v>
+      </c>
+      <c r="N37" s="19">
+        <v>17</v>
+      </c>
+      <c r="O37" s="19">
+        <v>14.5</v>
+      </c>
+      <c r="P37" s="19">
+        <v>15.438000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -7743,12 +7859,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A6DA72B-EEC5-42C3-B327-5A9F9ACABB0A}">
   <dimension ref="A1:Y8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.83203125" style="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.33203125" style="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.36328125" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1796875" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.81640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.36328125" style="18" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="19"/>
     <col min="26" max="16384" width="9" style="15"/>
   </cols>
@@ -8129,13 +8245,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54319F21-0FC0-45E2-9E0C-131772CB34B0}">
-  <dimension ref="A1:Y36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:Y37"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.33203125" style="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1796875" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.36328125" style="18" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="19"/>
     <col min="26" max="16384" width="9" style="15"/>
   </cols>
@@ -9785,6 +9901,47 @@
         <v>4.5</v>
       </c>
       <c r="M36" s="19">
+        <v>6.4870000000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="A37" s="16">
+        <v>46209</v>
+      </c>
+      <c r="B37" s="16">
+        <v>46216</v>
+      </c>
+      <c r="C37" s="17">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E37" s="19">
+        <v>20</v>
+      </c>
+      <c r="F37" s="19">
+        <v>15.5</v>
+      </c>
+      <c r="G37" s="19">
+        <v>19.292999999999999</v>
+      </c>
+      <c r="H37" s="19">
+        <v>11.3</v>
+      </c>
+      <c r="I37" s="19">
+        <v>8</v>
+      </c>
+      <c r="J37" s="19">
+        <v>10.18</v>
+      </c>
+      <c r="K37" s="19">
+        <v>8.9</v>
+      </c>
+      <c r="L37" s="19">
+        <v>4.5</v>
+      </c>
+      <c r="M37" s="19">
         <v>6.4870000000000001</v>
       </c>
     </row>
@@ -9802,15 +9959,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B53F4-91AF-4D49-84B3-FC7BC3C51C10}">
-  <dimension ref="A1:Y36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:Y37"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.33203125" style="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="13.1640625" style="19" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.1640625" style="19" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1796875" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.36328125" style="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="13.1796875" style="19" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.1796875" style="19" bestFit="1" customWidth="1"/>
     <col min="17" max="25" width="9" style="19"/>
     <col min="26" max="16384" width="9" style="15"/>
   </cols>
@@ -11739,6 +11896,56 @@
         <v>11.9</v>
       </c>
       <c r="P36" s="19">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37" s="16">
+        <v>46209</v>
+      </c>
+      <c r="B37" s="16">
+        <v>46216</v>
+      </c>
+      <c r="C37" s="17">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E37" s="19">
+        <v>3.1</v>
+      </c>
+      <c r="F37" s="19">
+        <v>2.8</v>
+      </c>
+      <c r="G37" s="19">
+        <v>2.9249999999999998</v>
+      </c>
+      <c r="H37" s="19">
+        <v>4.8</v>
+      </c>
+      <c r="I37" s="19">
+        <v>3.95</v>
+      </c>
+      <c r="J37" s="19">
+        <v>4.375</v>
+      </c>
+      <c r="K37" s="19">
+        <v>7.1</v>
+      </c>
+      <c r="L37" s="19">
+        <v>6.2</v>
+      </c>
+      <c r="M37" s="19">
+        <v>6.665</v>
+      </c>
+      <c r="N37" s="19">
+        <v>13.3</v>
+      </c>
+      <c r="O37" s="19">
+        <v>12</v>
+      </c>
+      <c r="P37" s="19">
         <v>12.6</v>
       </c>
     </row>
@@ -11757,14 +11964,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD3DFE18-E6A7-46E2-A20D-CA2E453C377B}">
   <dimension ref="A1:Y5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="13.1640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1796875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="13.1796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.1796875" style="9" bestFit="1" customWidth="1"/>
     <col min="17" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
@@ -12029,16 +12236,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A9E7BC-4FDA-42FF-94EB-B5FEB168C665}">
   <dimension ref="A1:AJ19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" style="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.36328125" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.36328125" style="17" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="22" width="10.33203125" style="19" customWidth="1"/>
-    <col min="23" max="24" width="7.83203125" style="19" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.33203125" style="19" bestFit="1" customWidth="1"/>
-    <col min="26" max="28" width="10.6640625" style="19" customWidth="1"/>
+    <col min="5" max="22" width="10.36328125" style="19" customWidth="1"/>
+    <col min="23" max="24" width="7.81640625" style="19" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.36328125" style="19" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="10.6328125" style="19" customWidth="1"/>
     <col min="29" max="36" width="9" style="19"/>
     <col min="37" max="16384" width="9" style="15"/>
   </cols>
@@ -13354,7 +13561,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{303223D0-B4CB-49AA-99CE-D17D229E45B9}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13366,11 +13573,11 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF9DD02-7584-4E7B-8430-E8812C31F69E}">
   <dimension ref="A1:C39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="28.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/data_lake/industry/TrendForce/NAND Flash.xlsx
+++ b/data_lake/industry/TrendForce/NAND Flash.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2557E368-B31A-4464-8E84-3F61AAFD8470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{695BC8D9-C786-4236-931F-83401DAC2C88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="76">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -436,21 +436,6 @@
     <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -472,6 +457,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
@@ -623,6 +623,9 @@
                 <c:pt idx="25">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="26">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -709,6 +712,9 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>4.0449999999999999</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>4.093</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -833,6 +839,9 @@
                 <c:pt idx="25">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="26">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -919,6 +928,9 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>3.573</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3.5379999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1043,6 +1055,9 @@
                 <c:pt idx="25">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="26">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1129,6 +1144,9 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>31.390999999999998</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>32.564999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1253,6 +1271,9 @@
                 <c:pt idx="25">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="26">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1339,6 +1360,9 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>15.55</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>15.938000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1715,6 +1739,9 @@
                 <c:pt idx="35">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="36">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1831,6 +1858,9 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>19.175999999999998</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>18.931000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1985,6 +2015,9 @@
                 <c:pt idx="35">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="36">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2101,6 +2134,9 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>10.18</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>10.464</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2255,6 +2291,9 @@
                 <c:pt idx="35">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="36">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2371,6 +2410,9 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>6.4870000000000001</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>6.6529999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2747,6 +2789,9 @@
                 <c:pt idx="35">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="36">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2862,6 +2907,9 @@
                   <c:v>2.9249999999999998</c:v>
                 </c:pt>
                 <c:pt idx="35">
+                  <c:v>2.9649999999999999</c:v>
+                </c:pt>
+                <c:pt idx="36">
                   <c:v>2.9649999999999999</c:v>
                 </c:pt>
               </c:numCache>
@@ -3017,6 +3065,9 @@
                 <c:pt idx="35">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="36">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3132,6 +3183,9 @@
                   <c:v>4.375</c:v>
                 </c:pt>
                 <c:pt idx="35">
+                  <c:v>4.45</c:v>
+                </c:pt>
+                <c:pt idx="36">
                   <c:v>4.45</c:v>
                 </c:pt>
               </c:numCache>
@@ -3287,6 +3341,9 @@
                 <c:pt idx="35">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="36">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3403,6 +3460,9 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>6.7249999999999996</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>6.7149999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3557,6 +3617,9 @@
                 <c:pt idx="35">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="36">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3673,6 +3736,9 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>12.625</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>12.55</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5937,7 +6003,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y38"/>
+  <dimension ref="A1:Y39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.796875" style="8" bestFit="1" customWidth="1"/>
@@ -5949,16 +6015,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="25" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
@@ -6008,10 +6074,10 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="16"/>
+      <c r="A2" s="23"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="25"/>
       <c r="E2" s="6" t="s">
         <v>4</v>
       </c>
@@ -7973,6 +8039,56 @@
       </c>
       <c r="P38" s="11">
         <v>15.55</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A39" s="8">
+        <v>46223</v>
+      </c>
+      <c r="B39" s="8">
+        <v>46230</v>
+      </c>
+      <c r="C39" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E39" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F39" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="G39" s="11">
+        <v>4.093</v>
+      </c>
+      <c r="H39" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="I39" s="11">
+        <v>3.15</v>
+      </c>
+      <c r="J39" s="11">
+        <v>3.5379999999999998</v>
+      </c>
+      <c r="K39" s="11">
+        <v>52</v>
+      </c>
+      <c r="L39" s="11">
+        <v>27</v>
+      </c>
+      <c r="M39" s="11">
+        <v>32.564999999999998</v>
+      </c>
+      <c r="N39" s="11">
+        <v>17</v>
+      </c>
+      <c r="O39" s="11">
+        <v>15.2</v>
+      </c>
+      <c r="P39" s="11">
+        <v>15.938000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -7993,25 +8109,25 @@
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.3984375" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="25" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
@@ -8055,10 +8171,10 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="16"/>
+      <c r="A2" s="23"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="25"/>
       <c r="E2" s="6" t="s">
         <v>4</v>
       </c>
@@ -8377,7 +8493,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54319F21-0FC0-45E2-9E0C-131772CB34B0}">
-  <dimension ref="A1:Y38"/>
+  <dimension ref="A1:Y39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.19921875" style="8" bestFit="1" customWidth="1"/>
@@ -8389,16 +8505,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="25" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
@@ -8442,10 +8558,10 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="16"/>
+      <c r="A2" s="23"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="25"/>
       <c r="E2" s="6" t="s">
         <v>4</v>
       </c>
@@ -10116,6 +10232,47 @@
       </c>
       <c r="M38" s="11">
         <v>6.4870000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A39" s="8">
+        <v>46223</v>
+      </c>
+      <c r="B39" s="8">
+        <v>46230</v>
+      </c>
+      <c r="C39" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E39" s="11">
+        <v>20</v>
+      </c>
+      <c r="F39" s="11">
+        <v>15</v>
+      </c>
+      <c r="G39" s="11">
+        <v>18.931000000000001</v>
+      </c>
+      <c r="H39" s="11">
+        <v>14</v>
+      </c>
+      <c r="I39" s="11">
+        <v>9</v>
+      </c>
+      <c r="J39" s="11">
+        <v>10.464</v>
+      </c>
+      <c r="K39" s="11">
+        <v>10</v>
+      </c>
+      <c r="L39" s="11">
+        <v>5</v>
+      </c>
+      <c r="M39" s="11">
+        <v>6.6529999999999996</v>
       </c>
     </row>
   </sheetData>
@@ -10132,7 +10289,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B53F4-91AF-4D49-84B3-FC7BC3C51C10}">
-  <dimension ref="A1:Y38"/>
+  <dimension ref="A1:Y39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.19921875" style="8" bestFit="1" customWidth="1"/>
@@ -10146,16 +10303,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="25" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
@@ -10205,10 +10362,10 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="16"/>
+      <c r="A2" s="23"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="25"/>
       <c r="E2" s="6" t="s">
         <v>4</v>
       </c>
@@ -12170,6 +12327,56 @@
       </c>
       <c r="P38" s="11">
         <v>12.625</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A39" s="8">
+        <v>46223</v>
+      </c>
+      <c r="B39" s="8">
+        <v>46230</v>
+      </c>
+      <c r="C39" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E39" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="F39" s="11">
+        <v>2.85</v>
+      </c>
+      <c r="G39" s="11">
+        <v>2.9649999999999999</v>
+      </c>
+      <c r="H39" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="I39" s="11">
+        <v>4</v>
+      </c>
+      <c r="J39" s="11">
+        <v>4.45</v>
+      </c>
+      <c r="K39" s="11">
+        <v>7.1</v>
+      </c>
+      <c r="L39" s="11">
+        <v>6.2</v>
+      </c>
+      <c r="M39" s="11">
+        <v>6.7149999999999999</v>
+      </c>
+      <c r="N39" s="11">
+        <v>13.2</v>
+      </c>
+      <c r="O39" s="11">
+        <v>12.1</v>
+      </c>
+      <c r="P39" s="11">
+        <v>12.55</v>
       </c>
     </row>
   </sheetData>
@@ -12189,258 +12396,258 @@
   <dimension ref="A1:Y5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.3984375" style="26" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="26" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.3984375" style="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="13.19921875" style="27" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.19921875" style="27" bestFit="1" customWidth="1"/>
-    <col min="17" max="25" width="9" style="27"/>
-    <col min="26" max="16384" width="9" style="23"/>
+    <col min="1" max="1" width="11.3984375" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.3984375" style="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="13.19921875" style="22" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.19921875" style="22" bestFit="1" customWidth="1"/>
+    <col min="17" max="25" width="9" style="22"/>
+    <col min="26" max="16384" width="9" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:25" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="J1" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="K1" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="L1" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="M1" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
-      <c r="X1" s="20"/>
-      <c r="Y1" s="20"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="22" t="s">
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="22" t="s">
+      <c r="G2" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="22" t="s">
+      <c r="I2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="22" t="s">
+      <c r="J2" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="22" t="s">
+      <c r="K2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="22" t="s">
+      <c r="L2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="22" t="s">
+      <c r="M2" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
-      <c r="U2" s="22"/>
-      <c r="V2" s="22"/>
-      <c r="W2" s="22"/>
-      <c r="X2" s="22"/>
-      <c r="Y2" s="22"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="17"/>
+      <c r="U2" s="17"/>
+      <c r="V2" s="17"/>
+      <c r="W2" s="17"/>
+      <c r="X2" s="17"/>
+      <c r="Y2" s="17"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A3" s="24">
+      <c r="A3" s="19">
         <v>45930</v>
       </c>
-      <c r="B3" s="24">
+      <c r="B3" s="19">
         <v>45953</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="20">
         <v>0.58333333333333337</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="17">
         <v>76</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="17">
         <v>70</v>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="17">
         <v>73.2</v>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="17">
         <v>48</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="17">
         <v>44</v>
       </c>
-      <c r="J3" s="22">
+      <c r="J3" s="17">
         <v>46.4</v>
       </c>
-      <c r="K3" s="22">
+      <c r="K3" s="17">
         <v>32</v>
       </c>
-      <c r="L3" s="22">
+      <c r="L3" s="17">
         <v>28</v>
       </c>
-      <c r="M3" s="22">
+      <c r="M3" s="17">
         <v>30</v>
       </c>
-      <c r="N3" s="22"/>
-      <c r="O3" s="22"/>
-      <c r="P3" s="22"/>
-      <c r="Q3" s="22"/>
-      <c r="R3" s="22"/>
-      <c r="S3" s="22"/>
-      <c r="T3" s="22"/>
-      <c r="U3" s="22"/>
-      <c r="V3" s="22"/>
-      <c r="W3" s="22"/>
-      <c r="X3" s="22"/>
-      <c r="Y3" s="22"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="17"/>
+      <c r="T3" s="17"/>
+      <c r="U3" s="17"/>
+      <c r="V3" s="17"/>
+      <c r="W3" s="17"/>
+      <c r="X3" s="17"/>
+      <c r="Y3" s="17"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A4" s="24">
+      <c r="A4" s="19">
         <v>46042</v>
       </c>
-      <c r="B4" s="24">
+      <c r="B4" s="19">
         <v>46048</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="20">
         <v>0.58333333333333337</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="17">
         <v>159</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="17">
         <v>149</v>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="17">
         <v>153.9</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="17">
         <v>100</v>
       </c>
-      <c r="I4" s="22">
+      <c r="I4" s="17">
         <v>94</v>
       </c>
-      <c r="J4" s="22">
+      <c r="J4" s="17">
         <v>97.1</v>
       </c>
-      <c r="K4" s="22">
+      <c r="K4" s="17">
         <v>65</v>
       </c>
-      <c r="L4" s="22">
+      <c r="L4" s="17">
         <v>58.5</v>
       </c>
-      <c r="M4" s="22">
+      <c r="M4" s="17">
         <v>61.3</v>
       </c>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
-      <c r="R4" s="22"/>
-      <c r="S4" s="22"/>
-      <c r="T4" s="22"/>
-      <c r="U4" s="22"/>
-      <c r="V4" s="22"/>
-      <c r="W4" s="22"/>
-      <c r="X4" s="22"/>
-      <c r="Y4" s="22"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="17"/>
+      <c r="U4" s="17"/>
+      <c r="V4" s="17"/>
+      <c r="W4" s="17"/>
+      <c r="X4" s="17"/>
+      <c r="Y4" s="17"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A5" s="24">
+      <c r="A5" s="19">
         <v>46139</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="19">
         <v>46139</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="20">
         <v>0.58333333333333337</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="22">
         <v>278</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="22">
         <v>265</v>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="22">
         <v>270.10000000000002</v>
       </c>
-      <c r="H5" s="27">
+      <c r="H5" s="22">
         <v>177</v>
       </c>
-      <c r="I5" s="27">
+      <c r="I5" s="22">
         <v>165</v>
       </c>
-      <c r="J5" s="27">
+      <c r="J5" s="22">
         <v>170.2</v>
       </c>
-      <c r="K5" s="27">
+      <c r="K5" s="22">
         <v>110</v>
       </c>
-      <c r="L5" s="27">
+      <c r="L5" s="22">
         <v>101</v>
       </c>
-      <c r="M5" s="27">
+      <c r="M5" s="22">
         <v>104.6</v>
       </c>
     </row>
@@ -12474,16 +12681,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="25" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
@@ -12568,10 +12775,10 @@
       <c r="AJ1" s="4"/>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="16"/>
+      <c r="A2" s="23"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="25"/>
       <c r="E2" s="6" t="s">
         <v>4</v>
       </c>

--- a/data_lake/industry/TrendForce/NAND Flash.xlsx
+++ b/data_lake/industry/TrendForce/NAND Flash.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{695BC8D9-C786-4236-931F-83401DAC2C88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6973FF80-EB43-4AAD-A2EE-717C07FE3676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="76">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -626,6 +626,9 @@
                 <c:pt idx="26">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="27">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -715,6 +718,9 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>4.093</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>4.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -842,6 +848,9 @@
                 <c:pt idx="26">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="27">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -931,6 +940,9 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>3.5379999999999998</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3.5150000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1058,6 +1070,9 @@
                 <c:pt idx="26">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="27">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1147,6 +1162,9 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>32.564999999999998</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>32.912999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1274,6 +1292,9 @@
                 <c:pt idx="26">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="27">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1363,6 +1384,9 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>15.938000000000001</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>16.100000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1742,6 +1766,9 @@
                 <c:pt idx="36">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="37">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1861,6 +1888,9 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>18.931000000000001</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>19.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2018,6 +2048,9 @@
                 <c:pt idx="36">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="37">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2137,6 +2170,9 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>10.464</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>10.787000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2294,6 +2330,9 @@
                 <c:pt idx="36">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="37">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2413,6 +2452,9 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>6.6529999999999996</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>6.8529999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2792,6 +2834,9 @@
                 <c:pt idx="36">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="37">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2910,6 +2955,9 @@
                   <c:v>2.9649999999999999</c:v>
                 </c:pt>
                 <c:pt idx="36">
+                  <c:v>2.9649999999999999</c:v>
+                </c:pt>
+                <c:pt idx="37">
                   <c:v>2.9649999999999999</c:v>
                 </c:pt>
               </c:numCache>
@@ -3068,6 +3116,9 @@
                 <c:pt idx="36">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="37">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3187,6 +3238,9 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>4.45</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>4.4249999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3344,6 +3398,9 @@
                 <c:pt idx="36">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="37">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3463,6 +3520,9 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>6.7149999999999999</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>6.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3620,6 +3680,9 @@
                 <c:pt idx="36">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="37">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3739,6 +3802,9 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>12.55</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>12.45</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6003,7 +6069,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y39"/>
+  <dimension ref="A1:Y40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.796875" style="8" bestFit="1" customWidth="1"/>
@@ -8089,6 +8155,56 @@
       </c>
       <c r="P39" s="11">
         <v>15.938000000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A40" s="8">
+        <v>46230</v>
+      </c>
+      <c r="B40" s="8">
+        <v>46237</v>
+      </c>
+      <c r="C40" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E40" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F40" s="11">
+        <v>3.9</v>
+      </c>
+      <c r="G40" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="H40" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="I40" s="11">
+        <v>3.15</v>
+      </c>
+      <c r="J40" s="11">
+        <v>3.5150000000000001</v>
+      </c>
+      <c r="K40" s="11">
+        <v>53</v>
+      </c>
+      <c r="L40" s="11">
+        <v>27.5</v>
+      </c>
+      <c r="M40" s="11">
+        <v>32.912999999999997</v>
+      </c>
+      <c r="N40" s="11">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="O40" s="11">
+        <v>15.3</v>
+      </c>
+      <c r="P40" s="11">
+        <v>16.100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -8106,7 +8222,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A6DA72B-EEC5-42C3-B327-5A9F9ACABB0A}">
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.796875" style="8" bestFit="1" customWidth="1"/>
@@ -8477,6 +8593,47 @@
       </c>
       <c r="M8" s="11">
         <v>15.493</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A9" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B9" s="8">
+        <v>46234</v>
+      </c>
+      <c r="C9" s="9">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="11">
+        <v>29.1</v>
+      </c>
+      <c r="F9" s="11">
+        <v>28.4</v>
+      </c>
+      <c r="G9" s="11">
+        <v>28.82</v>
+      </c>
+      <c r="H9" s="11">
+        <v>22</v>
+      </c>
+      <c r="I9" s="11">
+        <v>20.8</v>
+      </c>
+      <c r="J9" s="11">
+        <v>21.364999999999998</v>
+      </c>
+      <c r="K9" s="11">
+        <v>17.2</v>
+      </c>
+      <c r="L9" s="11">
+        <v>16.8</v>
+      </c>
+      <c r="M9" s="11">
+        <v>17.074999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -8493,7 +8650,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54319F21-0FC0-45E2-9E0C-131772CB34B0}">
-  <dimension ref="A1:Y39"/>
+  <dimension ref="A1:Y40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.19921875" style="8" bestFit="1" customWidth="1"/>
@@ -10273,6 +10430,47 @@
       </c>
       <c r="M39" s="11">
         <v>6.6529999999999996</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A40" s="8">
+        <v>46230</v>
+      </c>
+      <c r="B40" s="8">
+        <v>46237</v>
+      </c>
+      <c r="C40" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E40" s="11">
+        <v>22</v>
+      </c>
+      <c r="F40" s="11">
+        <v>16</v>
+      </c>
+      <c r="G40" s="11">
+        <v>19.25</v>
+      </c>
+      <c r="H40" s="11">
+        <v>15</v>
+      </c>
+      <c r="I40" s="11">
+        <v>10</v>
+      </c>
+      <c r="J40" s="11">
+        <v>10.787000000000001</v>
+      </c>
+      <c r="K40" s="11">
+        <v>10</v>
+      </c>
+      <c r="L40" s="11">
+        <v>5.3</v>
+      </c>
+      <c r="M40" s="11">
+        <v>6.8529999999999998</v>
       </c>
     </row>
   </sheetData>
@@ -10289,7 +10487,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B53F4-91AF-4D49-84B3-FC7BC3C51C10}">
-  <dimension ref="A1:Y39"/>
+  <dimension ref="A1:Y40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.19921875" style="8" bestFit="1" customWidth="1"/>
@@ -12377,6 +12575,56 @@
       </c>
       <c r="P39" s="11">
         <v>12.55</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A40" s="8">
+        <v>46230</v>
+      </c>
+      <c r="B40" s="8">
+        <v>46237</v>
+      </c>
+      <c r="C40" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E40" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="F40" s="11">
+        <v>2.85</v>
+      </c>
+      <c r="G40" s="11">
+        <v>2.9649999999999999</v>
+      </c>
+      <c r="H40" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="I40" s="11">
+        <v>4</v>
+      </c>
+      <c r="J40" s="11">
+        <v>4.4249999999999998</v>
+      </c>
+      <c r="K40" s="11">
+        <v>7.1</v>
+      </c>
+      <c r="L40" s="11">
+        <v>6.2</v>
+      </c>
+      <c r="M40" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="N40" s="11">
+        <v>13</v>
+      </c>
+      <c r="O40" s="11">
+        <v>12.1</v>
+      </c>
+      <c r="P40" s="11">
+        <v>12.45</v>
       </c>
     </row>
   </sheetData>
@@ -12665,7 +12913,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A9E7BC-4FDA-42FF-94EB-B5FEB168C665}">
-  <dimension ref="A1:AJ20"/>
+  <dimension ref="A1:AJ21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.3984375" style="8" bestFit="1" customWidth="1"/>
@@ -14033,6 +14281,65 @@
       </c>
       <c r="V20" s="11">
         <v>165.97</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A21" s="8">
+        <v>46234</v>
+      </c>
+      <c r="B21" s="8">
+        <v>46234</v>
+      </c>
+      <c r="C21" s="9">
+        <v>0.4375</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" s="11">
+        <v>242</v>
+      </c>
+      <c r="F21" s="11">
+        <v>242</v>
+      </c>
+      <c r="G21" s="11">
+        <v>242</v>
+      </c>
+      <c r="H21" s="11">
+        <v>152.6</v>
+      </c>
+      <c r="I21" s="11">
+        <v>117.5</v>
+      </c>
+      <c r="J21" s="11">
+        <v>135</v>
+      </c>
+      <c r="K21" s="11">
+        <v>238.88</v>
+      </c>
+      <c r="L21" s="11">
+        <v>238.88</v>
+      </c>
+      <c r="M21" s="11">
+        <v>238.88</v>
+      </c>
+      <c r="Q21" s="11">
+        <v>395</v>
+      </c>
+      <c r="R21" s="11">
+        <v>395</v>
+      </c>
+      <c r="S21" s="11">
+        <v>395</v>
+      </c>
+      <c r="T21" s="11">
+        <v>164.97</v>
+      </c>
+      <c r="U21" s="11">
+        <v>164.97</v>
+      </c>
+      <c r="V21" s="11">
+        <v>164.97</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/industry/TrendForce/NAND Flash.xlsx
+++ b/data_lake/industry/TrendForce/NAND Flash.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6973FF80-EB43-4AAD-A2EE-717C07FE3676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C0E0147-67AC-4600-8E89-427AC469C896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="76">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -629,6 +629,9 @@
                 <c:pt idx="27">
                   <c:v>46237</c:v>
                 </c:pt>
+                <c:pt idx="28">
+                  <c:v>46244</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -721,6 +724,9 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>4.2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>4.2750000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -851,6 +857,9 @@
                 <c:pt idx="27">
                   <c:v>46237</c:v>
                 </c:pt>
+                <c:pt idx="28">
+                  <c:v>46244</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -943,6 +952,9 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>3.5150000000000001</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3.5249999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1073,6 +1085,9 @@
                 <c:pt idx="27">
                   <c:v>46237</c:v>
                 </c:pt>
+                <c:pt idx="28">
+                  <c:v>46244</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1165,6 +1180,9 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>32.912999999999997</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>34.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1295,6 +1313,9 @@
                 <c:pt idx="27">
                   <c:v>46237</c:v>
                 </c:pt>
+                <c:pt idx="28">
+                  <c:v>46244</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1387,6 +1408,9 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>16.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>16.937999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1769,6 +1793,9 @@
                 <c:pt idx="37">
                   <c:v>46237</c:v>
                 </c:pt>
+                <c:pt idx="38">
+                  <c:v>46244</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1891,6 +1918,9 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>19.25</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>20.125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2051,6 +2081,9 @@
                 <c:pt idx="37">
                   <c:v>46237</c:v>
                 </c:pt>
+                <c:pt idx="38">
+                  <c:v>46244</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2173,6 +2206,9 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>10.787000000000001</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>12.538</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2333,6 +2369,9 @@
                 <c:pt idx="37">
                   <c:v>46237</c:v>
                 </c:pt>
+                <c:pt idx="38">
+                  <c:v>46244</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2455,6 +2494,9 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>6.8529999999999998</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>7.8330000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2837,6 +2879,9 @@
                 <c:pt idx="37">
                   <c:v>46237</c:v>
                 </c:pt>
+                <c:pt idx="38">
+                  <c:v>46244</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2958,6 +3003,9 @@
                   <c:v>2.9649999999999999</c:v>
                 </c:pt>
                 <c:pt idx="37">
+                  <c:v>2.9649999999999999</c:v>
+                </c:pt>
+                <c:pt idx="38">
                   <c:v>2.9649999999999999</c:v>
                 </c:pt>
               </c:numCache>
@@ -3119,6 +3167,9 @@
                 <c:pt idx="37">
                   <c:v>46237</c:v>
                 </c:pt>
+                <c:pt idx="38">
+                  <c:v>46244</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3241,6 +3292,9 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>4.4249999999999998</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>4.375</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3401,6 +3455,9 @@
                 <c:pt idx="37">
                   <c:v>46237</c:v>
                 </c:pt>
+                <c:pt idx="38">
+                  <c:v>46244</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3523,6 +3580,9 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>6.7</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>6.6749999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3683,6 +3743,9 @@
                 <c:pt idx="37">
                   <c:v>46237</c:v>
                 </c:pt>
+                <c:pt idx="38">
+                  <c:v>46244</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3804,6 +3867,9 @@
                   <c:v>12.55</c:v>
                 </c:pt>
                 <c:pt idx="37">
+                  <c:v>12.45</c:v>
+                </c:pt>
+                <c:pt idx="38">
                   <c:v>12.45</c:v>
                 </c:pt>
               </c:numCache>
@@ -6069,7 +6135,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y40"/>
+  <dimension ref="A1:Y41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.796875" style="8" bestFit="1" customWidth="1"/>
@@ -8205,6 +8271,56 @@
       </c>
       <c r="P40" s="11">
         <v>16.100000000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A41" s="8">
+        <v>46237</v>
+      </c>
+      <c r="B41" s="8">
+        <v>46244</v>
+      </c>
+      <c r="C41" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E41" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="F41" s="11">
+        <v>3.95</v>
+      </c>
+      <c r="G41" s="11">
+        <v>4.2750000000000004</v>
+      </c>
+      <c r="H41" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="I41" s="11">
+        <v>3.15</v>
+      </c>
+      <c r="J41" s="11">
+        <v>3.5249999999999999</v>
+      </c>
+      <c r="K41" s="11">
+        <v>55</v>
+      </c>
+      <c r="L41" s="11">
+        <v>29</v>
+      </c>
+      <c r="M41" s="11">
+        <v>34.75</v>
+      </c>
+      <c r="N41" s="11">
+        <v>18.5</v>
+      </c>
+      <c r="O41" s="11">
+        <v>16</v>
+      </c>
+      <c r="P41" s="11">
+        <v>16.937999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -8650,7 +8766,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54319F21-0FC0-45E2-9E0C-131772CB34B0}">
-  <dimension ref="A1:Y40"/>
+  <dimension ref="A1:Y41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.19921875" style="8" bestFit="1" customWidth="1"/>
@@ -10471,6 +10587,47 @@
       </c>
       <c r="M40" s="11">
         <v>6.8529999999999998</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A41" s="8">
+        <v>46237</v>
+      </c>
+      <c r="B41" s="8">
+        <v>46244</v>
+      </c>
+      <c r="C41" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E41" s="11">
+        <v>23</v>
+      </c>
+      <c r="F41" s="11">
+        <v>17</v>
+      </c>
+      <c r="G41" s="11">
+        <v>20.125</v>
+      </c>
+      <c r="H41" s="11">
+        <v>16</v>
+      </c>
+      <c r="I41" s="11">
+        <v>11.5</v>
+      </c>
+      <c r="J41" s="11">
+        <v>12.538</v>
+      </c>
+      <c r="K41" s="11">
+        <v>12</v>
+      </c>
+      <c r="L41" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="M41" s="11">
+        <v>7.8330000000000002</v>
       </c>
     </row>
   </sheetData>
@@ -10487,7 +10644,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B53F4-91AF-4D49-84B3-FC7BC3C51C10}">
-  <dimension ref="A1:Y40"/>
+  <dimension ref="A1:Y41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.19921875" style="8" bestFit="1" customWidth="1"/>
@@ -12624,6 +12781,56 @@
         <v>12.1</v>
       </c>
       <c r="P40" s="11">
+        <v>12.45</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A41" s="8">
+        <v>46237</v>
+      </c>
+      <c r="B41" s="8">
+        <v>46244</v>
+      </c>
+      <c r="C41" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E41" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="F41" s="11">
+        <v>2.85</v>
+      </c>
+      <c r="G41" s="11">
+        <v>2.9649999999999999</v>
+      </c>
+      <c r="H41" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="I41" s="11">
+        <v>4</v>
+      </c>
+      <c r="J41" s="11">
+        <v>4.375</v>
+      </c>
+      <c r="K41" s="11">
+        <v>7.1</v>
+      </c>
+      <c r="L41" s="11">
+        <v>6.2</v>
+      </c>
+      <c r="M41" s="11">
+        <v>6.6749999999999998</v>
+      </c>
+      <c r="N41" s="11">
+        <v>13</v>
+      </c>
+      <c r="O41" s="11">
+        <v>12.1</v>
+      </c>
+      <c r="P41" s="11">
         <v>12.45</v>
       </c>
     </row>

--- a/data_lake/industry/TrendForce/NAND Flash.xlsx
+++ b/data_lake/industry/TrendForce/NAND Flash.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C0E0147-67AC-4600-8E89-427AC469C896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D6E458-31F2-2A4E-B3B3-D3E008130673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25640" yWindow="600" windowWidth="25560" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="76">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -305,23 +305,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -334,7 +334,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -397,7 +397,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -412,55 +412,55 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -469,13 +469,13 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -493,7 +493,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -632,6 +632,9 @@
                 <c:pt idx="28">
                   <c:v>46244</c:v>
                 </c:pt>
+                <c:pt idx="29">
+                  <c:v>46251</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -727,6 +730,9 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>4.2750000000000004</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>4.3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -860,6 +866,9 @@
                 <c:pt idx="28">
                   <c:v>46244</c:v>
                 </c:pt>
+                <c:pt idx="29">
+                  <c:v>46251</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -955,6 +964,9 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>3.5249999999999999</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3.4950000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1088,6 +1100,9 @@
                 <c:pt idx="28">
                   <c:v>46244</c:v>
                 </c:pt>
+                <c:pt idx="29">
+                  <c:v>46251</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1183,6 +1198,9 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>34.75</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>35.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1316,6 +1334,9 @@
                 <c:pt idx="28">
                   <c:v>46244</c:v>
                 </c:pt>
+                <c:pt idx="29">
+                  <c:v>46251</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1411,6 +1432,9 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>16.937999999999999</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>17.437999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1627,7 +1651,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1796,6 +1820,9 @@
                 <c:pt idx="38">
                   <c:v>46244</c:v>
                 </c:pt>
+                <c:pt idx="39">
+                  <c:v>46251</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1921,6 +1948,9 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>20.125</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>21.125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2084,6 +2114,9 @@
                 <c:pt idx="38">
                   <c:v>46244</c:v>
                 </c:pt>
+                <c:pt idx="39">
+                  <c:v>46251</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2209,6 +2242,9 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>12.538</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>14.731</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2372,6 +2408,9 @@
                 <c:pt idx="38">
                   <c:v>46244</c:v>
                 </c:pt>
+                <c:pt idx="39">
+                  <c:v>46251</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2497,6 +2536,9 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>7.8330000000000002</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2713,7 +2755,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2882,6 +2924,9 @@
                 <c:pt idx="38">
                   <c:v>46244</c:v>
                 </c:pt>
+                <c:pt idx="39">
+                  <c:v>46251</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3006,6 +3051,9 @@
                   <c:v>2.9649999999999999</c:v>
                 </c:pt>
                 <c:pt idx="38">
+                  <c:v>2.9649999999999999</c:v>
+                </c:pt>
+                <c:pt idx="39">
                   <c:v>2.9649999999999999</c:v>
                 </c:pt>
               </c:numCache>
@@ -3170,6 +3218,9 @@
                 <c:pt idx="38">
                   <c:v>46244</c:v>
                 </c:pt>
+                <c:pt idx="39">
+                  <c:v>46251</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3294,6 +3345,9 @@
                   <c:v>4.4249999999999998</c:v>
                 </c:pt>
                 <c:pt idx="38">
+                  <c:v>4.375</c:v>
+                </c:pt>
+                <c:pt idx="39">
                   <c:v>4.375</c:v>
                 </c:pt>
               </c:numCache>
@@ -3458,6 +3512,9 @@
                 <c:pt idx="38">
                   <c:v>46244</c:v>
                 </c:pt>
+                <c:pt idx="39">
+                  <c:v>46251</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3583,6 +3640,9 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>6.6749999999999998</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>6.65</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3746,6 +3806,9 @@
                 <c:pt idx="38">
                   <c:v>46244</c:v>
                 </c:pt>
+                <c:pt idx="39">
+                  <c:v>46251</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3871,6 +3934,9 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>12.45</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>12.425000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6135,18 +6201,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Y42"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.796875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.59765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -6205,7 +6271,7 @@
       <c r="X1" s="4"/>
       <c r="Y1" s="4"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25">
       <c r="A2" s="23"/>
       <c r="B2" s="23"/>
       <c r="C2" s="24"/>
@@ -6256,7 +6322,7 @@
       <c r="X2" s="6"/>
       <c r="Y2" s="6"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25">
       <c r="A3" s="8">
         <v>45964</v>
       </c>
@@ -6315,7 +6381,7 @@
       <c r="X3" s="6"/>
       <c r="Y3" s="6"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25">
       <c r="A4" s="8">
         <v>45971</v>
       </c>
@@ -6374,7 +6440,7 @@
       <c r="X4" s="6"/>
       <c r="Y4" s="6"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25">
       <c r="A5" s="8">
         <v>45978</v>
       </c>
@@ -6433,7 +6499,7 @@
       <c r="X5" s="6"/>
       <c r="Y5" s="6"/>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25">
       <c r="A6" s="8">
         <v>45985</v>
       </c>
@@ -6492,7 +6558,7 @@
       <c r="X6" s="6"/>
       <c r="Y6" s="6"/>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25">
       <c r="A7" s="8">
         <v>45992</v>
       </c>
@@ -6551,7 +6617,7 @@
       <c r="X7" s="6"/>
       <c r="Y7" s="6"/>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25">
       <c r="A8" s="8">
         <v>45999</v>
       </c>
@@ -6610,7 +6676,7 @@
       <c r="X8" s="6"/>
       <c r="Y8" s="6"/>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25">
       <c r="A9" s="8">
         <v>46006</v>
       </c>
@@ -6669,7 +6735,7 @@
       <c r="X9" s="6"/>
       <c r="Y9" s="6"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25">
       <c r="A10" s="8">
         <v>46013</v>
       </c>
@@ -6728,7 +6794,7 @@
       <c r="X10" s="6"/>
       <c r="Y10" s="6"/>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25">
       <c r="A11" s="8">
         <v>46020</v>
       </c>
@@ -6787,7 +6853,7 @@
       <c r="X11" s="6"/>
       <c r="Y11" s="6"/>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25">
       <c r="A12" s="8">
         <v>46027</v>
       </c>
@@ -6846,7 +6912,7 @@
       <c r="X12" s="6"/>
       <c r="Y12" s="6"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25">
       <c r="A13" s="8">
         <v>46034</v>
       </c>
@@ -6905,7 +6971,7 @@
       <c r="X13" s="6"/>
       <c r="Y13" s="6"/>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25">
       <c r="A14" s="8">
         <v>46041</v>
       </c>
@@ -6964,7 +7030,7 @@
       <c r="X14" s="6"/>
       <c r="Y14" s="6"/>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25">
       <c r="A15" s="8">
         <v>46048</v>
       </c>
@@ -7023,7 +7089,7 @@
       <c r="X15" s="6"/>
       <c r="Y15" s="6"/>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25">
       <c r="A16" s="8">
         <v>46055</v>
       </c>
@@ -7073,7 +7139,7 @@
         <v>4.9729999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16">
       <c r="A17" s="8">
         <v>46062</v>
       </c>
@@ -7123,7 +7189,7 @@
         <v>5.2450000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16">
       <c r="A18" s="8">
         <v>46076</v>
       </c>
@@ -7173,7 +7239,7 @@
         <v>5.4820000000000002</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16">
       <c r="A19" s="8">
         <v>46083</v>
       </c>
@@ -7223,7 +7289,7 @@
         <v>5.8179999999999996</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16">
       <c r="A20" s="8">
         <v>46090</v>
       </c>
@@ -7273,7 +7339,7 @@
         <v>6.2910000000000004</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16">
       <c r="A21" s="8">
         <v>46097</v>
       </c>
@@ -7323,7 +7389,7 @@
         <v>6.9329999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16">
       <c r="A22" s="8">
         <v>46104</v>
       </c>
@@ -7373,7 +7439,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16">
       <c r="A23" s="8">
         <v>46111</v>
       </c>
@@ -7423,7 +7489,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16">
       <c r="A24" s="8">
         <v>46118</v>
       </c>
@@ -7473,7 +7539,7 @@
         <v>8.6669999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16">
       <c r="A25" s="8">
         <v>46125</v>
       </c>
@@ -7523,7 +7589,7 @@
         <v>9.3670000000000009</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16">
       <c r="A26" s="8">
         <v>46132</v>
       </c>
@@ -7573,7 +7639,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16">
       <c r="A27" s="8">
         <v>46139</v>
       </c>
@@ -7623,7 +7689,7 @@
         <v>10.433</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16">
       <c r="A28" s="8">
         <v>46146</v>
       </c>
@@ -7673,7 +7739,7 @@
         <v>10.467000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16">
       <c r="A29" s="8">
         <v>46153</v>
       </c>
@@ -7723,7 +7789,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16">
       <c r="A30" s="8">
         <v>46160</v>
       </c>
@@ -7773,7 +7839,7 @@
         <v>11.266999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16">
       <c r="A31" s="8">
         <v>46167</v>
       </c>
@@ -7823,7 +7889,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16">
       <c r="A32" s="8">
         <v>46174</v>
       </c>
@@ -7873,7 +7939,7 @@
         <v>12.233000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16">
       <c r="A33" s="8">
         <v>46181</v>
       </c>
@@ -7923,7 +7989,7 @@
         <v>13.266999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16">
       <c r="A34" s="8">
         <v>46188</v>
       </c>
@@ -7973,7 +8039,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16">
       <c r="A35" s="8">
         <v>46195</v>
       </c>
@@ -8023,7 +8089,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16">
       <c r="A36" s="8">
         <v>46202</v>
       </c>
@@ -8073,7 +8139,7 @@
         <v>14.733000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16">
       <c r="A37" s="8">
         <v>46209</v>
       </c>
@@ -8123,7 +8189,7 @@
         <v>15.438000000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16">
       <c r="A38" s="8">
         <v>46216</v>
       </c>
@@ -8173,7 +8239,7 @@
         <v>15.55</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16">
       <c r="A39" s="8">
         <v>46223</v>
       </c>
@@ -8223,7 +8289,7 @@
         <v>15.938000000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16">
       <c r="A40" s="8">
         <v>46230</v>
       </c>
@@ -8273,7 +8339,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16">
       <c r="A41" s="8">
         <v>46237</v>
       </c>
@@ -8321,6 +8387,56 @@
       </c>
       <c r="P41" s="11">
         <v>16.937999999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42" s="8">
+        <v>46244</v>
+      </c>
+      <c r="B42" s="8">
+        <v>46251</v>
+      </c>
+      <c r="C42" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E42" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="F42" s="11">
+        <v>4</v>
+      </c>
+      <c r="G42" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="H42" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="I42" s="11">
+        <v>3.15</v>
+      </c>
+      <c r="J42" s="11">
+        <v>3.4950000000000001</v>
+      </c>
+      <c r="K42" s="11">
+        <v>55</v>
+      </c>
+      <c r="L42" s="11">
+        <v>31</v>
+      </c>
+      <c r="M42" s="11">
+        <v>35.75</v>
+      </c>
+      <c r="N42" s="11">
+        <v>19</v>
+      </c>
+      <c r="O42" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="P42" s="11">
+        <v>17.437999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -8339,17 +8455,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A6DA72B-EEC5-42C3-B327-5A9F9ACABB0A}">
   <dimension ref="A1:Y9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.3984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -8402,7 +8518,7 @@
       <c r="X1" s="4"/>
       <c r="Y1" s="4"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25">
       <c r="A2" s="23"/>
       <c r="B2" s="23"/>
       <c r="C2" s="24"/>
@@ -8447,7 +8563,7 @@
       <c r="X2" s="6"/>
       <c r="Y2" s="6"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25">
       <c r="A3" s="8">
         <v>46022</v>
       </c>
@@ -8494,7 +8610,7 @@
       <c r="X3" s="6"/>
       <c r="Y3" s="6"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25">
       <c r="A4" s="8">
         <v>46052</v>
       </c>
@@ -8547,7 +8663,7 @@
       <c r="X4" s="6"/>
       <c r="Y4" s="6"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25">
       <c r="A5" s="8">
         <v>46079</v>
       </c>
@@ -8588,7 +8704,7 @@
         <v>7.2080000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25">
       <c r="A6" s="8">
         <v>46112</v>
       </c>
@@ -8629,7 +8745,7 @@
         <v>10.45</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25">
       <c r="A7" s="8">
         <v>46142</v>
       </c>
@@ -8670,7 +8786,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25">
       <c r="A8" s="8">
         <v>46171</v>
       </c>
@@ -8711,7 +8827,7 @@
         <v>15.493</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25">
       <c r="A9" s="8">
         <v>46203</v>
       </c>
@@ -8766,18 +8882,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54319F21-0FC0-45E2-9E0C-131772CB34B0}">
-  <dimension ref="A1:Y41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Y42"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.3984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -8830,7 +8946,7 @@
       <c r="X1" s="4"/>
       <c r="Y1" s="4"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25">
       <c r="A2" s="23"/>
       <c r="B2" s="23"/>
       <c r="C2" s="24"/>
@@ -8875,7 +8991,7 @@
       <c r="X2" s="6"/>
       <c r="Y2" s="6"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25">
       <c r="A3" s="8">
         <v>45964</v>
       </c>
@@ -8928,7 +9044,7 @@
       <c r="X3" s="6"/>
       <c r="Y3" s="6"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25">
       <c r="A4" s="8">
         <v>45971</v>
       </c>
@@ -8981,7 +9097,7 @@
       <c r="X4" s="6"/>
       <c r="Y4" s="6"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25">
       <c r="A5" s="8">
         <v>45978</v>
       </c>
@@ -9034,7 +9150,7 @@
       <c r="X5" s="6"/>
       <c r="Y5" s="6"/>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25">
       <c r="A6" s="8">
         <v>45985</v>
       </c>
@@ -9087,7 +9203,7 @@
       <c r="X6" s="6"/>
       <c r="Y6" s="6"/>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25">
       <c r="A7" s="8">
         <v>45992</v>
       </c>
@@ -9140,7 +9256,7 @@
       <c r="X7" s="6"/>
       <c r="Y7" s="6"/>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25">
       <c r="A8" s="8">
         <v>45999</v>
       </c>
@@ -9193,7 +9309,7 @@
       <c r="X8" s="6"/>
       <c r="Y8" s="6"/>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25">
       <c r="A9" s="8">
         <v>46006</v>
       </c>
@@ -9246,7 +9362,7 @@
       <c r="X9" s="6"/>
       <c r="Y9" s="6"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25">
       <c r="A10" s="8">
         <v>46013</v>
       </c>
@@ -9299,7 +9415,7 @@
       <c r="X10" s="6"/>
       <c r="Y10" s="6"/>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25">
       <c r="A11" s="8">
         <v>46020</v>
       </c>
@@ -9352,7 +9468,7 @@
       <c r="X11" s="6"/>
       <c r="Y11" s="6"/>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25">
       <c r="A12" s="8">
         <v>46027</v>
       </c>
@@ -9405,7 +9521,7 @@
       <c r="X12" s="6"/>
       <c r="Y12" s="6"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25">
       <c r="A13" s="8">
         <v>46034</v>
       </c>
@@ -9458,7 +9574,7 @@
       <c r="X13" s="6"/>
       <c r="Y13" s="6"/>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25">
       <c r="A14" s="8">
         <v>46041</v>
       </c>
@@ -9511,7 +9627,7 @@
       <c r="X14" s="6"/>
       <c r="Y14" s="6"/>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25">
       <c r="A15" s="8">
         <v>46048</v>
       </c>
@@ -9564,7 +9680,7 @@
       <c r="X15" s="6"/>
       <c r="Y15" s="6"/>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25">
       <c r="A16" s="8">
         <v>46055</v>
       </c>
@@ -9605,7 +9721,7 @@
         <v>5.5170000000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13">
       <c r="A17" s="8">
         <v>46062</v>
       </c>
@@ -9646,7 +9762,7 @@
         <v>5.5170000000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13">
       <c r="A18" s="8">
         <v>46076</v>
       </c>
@@ -9687,7 +9803,7 @@
         <v>5.5170000000000003</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13">
       <c r="A19" s="8">
         <v>46083</v>
       </c>
@@ -9728,7 +9844,7 @@
         <v>6.45</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13">
       <c r="A20" s="8">
         <v>46090</v>
       </c>
@@ -9769,7 +9885,7 @@
         <v>6.9669999999999996</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13">
       <c r="A21" s="8">
         <v>46097</v>
       </c>
@@ -9810,7 +9926,7 @@
         <v>6.9669999999999996</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13">
       <c r="A22" s="8">
         <v>46104</v>
       </c>
@@ -9851,7 +9967,7 @@
         <v>6.9669999999999996</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13">
       <c r="A23" s="8">
         <v>46111</v>
       </c>
@@ -9892,7 +10008,7 @@
         <v>6.8330000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13">
       <c r="A24" s="8">
         <v>46118</v>
       </c>
@@ -9933,7 +10049,7 @@
         <v>6.8330000000000002</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13">
       <c r="A25" s="8">
         <v>46125</v>
       </c>
@@ -9974,7 +10090,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13">
       <c r="A26" s="8">
         <v>46132</v>
       </c>
@@ -10015,7 +10131,7 @@
         <v>6.58</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13">
       <c r="A27" s="8">
         <v>46139</v>
       </c>
@@ -10056,7 +10172,7 @@
         <v>6.58</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13">
       <c r="A28" s="8">
         <v>46146</v>
       </c>
@@ -10097,7 +10213,7 @@
         <v>6.58</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13">
       <c r="A29" s="8">
         <v>46153</v>
       </c>
@@ -10138,7 +10254,7 @@
         <v>6.58</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13">
       <c r="A30" s="8">
         <v>46160</v>
       </c>
@@ -10179,7 +10295,7 @@
         <v>6.58</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13">
       <c r="A31" s="8">
         <v>46167</v>
       </c>
@@ -10220,7 +10336,7 @@
         <v>6.58</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13">
       <c r="A32" s="8">
         <v>46174</v>
       </c>
@@ -10261,7 +10377,7 @@
         <v>6.58</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13">
       <c r="A33" s="8">
         <v>46181</v>
       </c>
@@ -10302,7 +10418,7 @@
         <v>6.58</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13">
       <c r="A34" s="8">
         <v>46188</v>
       </c>
@@ -10343,7 +10459,7 @@
         <v>6.55</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13">
       <c r="A35" s="8">
         <v>46195</v>
       </c>
@@ -10384,7 +10500,7 @@
         <v>6.4870000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13">
       <c r="A36" s="8">
         <v>46202</v>
       </c>
@@ -10425,7 +10541,7 @@
         <v>6.4870000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13">
       <c r="A37" s="8">
         <v>46209</v>
       </c>
@@ -10466,7 +10582,7 @@
         <v>6.4870000000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13">
       <c r="A38" s="8">
         <v>46216</v>
       </c>
@@ -10507,7 +10623,7 @@
         <v>6.4870000000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13">
       <c r="A39" s="8">
         <v>46223</v>
       </c>
@@ -10548,7 +10664,7 @@
         <v>6.6529999999999996</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13">
       <c r="A40" s="8">
         <v>46230</v>
       </c>
@@ -10589,7 +10705,7 @@
         <v>6.8529999999999998</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13">
       <c r="A41" s="8">
         <v>46237</v>
       </c>
@@ -10628,6 +10744,47 @@
       </c>
       <c r="M41" s="11">
         <v>7.8330000000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
+      <c r="A42" s="8">
+        <v>46244</v>
+      </c>
+      <c r="B42" s="8">
+        <v>46251</v>
+      </c>
+      <c r="C42" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E42" s="11">
+        <v>23</v>
+      </c>
+      <c r="F42" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="G42" s="11">
+        <v>21.125</v>
+      </c>
+      <c r="H42" s="11">
+        <v>18</v>
+      </c>
+      <c r="I42" s="11">
+        <v>12</v>
+      </c>
+      <c r="J42" s="11">
+        <v>14.731</v>
+      </c>
+      <c r="K42" s="11">
+        <v>15</v>
+      </c>
+      <c r="L42" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="M42" s="11">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -10644,20 +10801,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B53F4-91AF-4D49-84B3-FC7BC3C51C10}">
-  <dimension ref="A1:Y41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Y42"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.3984375" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="13.19921875" style="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="13.1640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.1640625" style="11" bestFit="1" customWidth="1"/>
     <col min="17" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -10716,7 +10873,7 @@
       <c r="X1" s="4"/>
       <c r="Y1" s="4"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25">
       <c r="A2" s="23"/>
       <c r="B2" s="23"/>
       <c r="C2" s="24"/>
@@ -10767,7 +10924,7 @@
       <c r="X2" s="6"/>
       <c r="Y2" s="6"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25">
       <c r="A3" s="8">
         <v>45964</v>
       </c>
@@ -10826,7 +10983,7 @@
       <c r="X3" s="6"/>
       <c r="Y3" s="6"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25">
       <c r="A4" s="8">
         <v>45971</v>
       </c>
@@ -10885,7 +11042,7 @@
       <c r="X4" s="6"/>
       <c r="Y4" s="6"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25">
       <c r="A5" s="8">
         <v>45978</v>
       </c>
@@ -10944,7 +11101,7 @@
       <c r="X5" s="6"/>
       <c r="Y5" s="6"/>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25">
       <c r="A6" s="8">
         <v>45985</v>
       </c>
@@ -11003,7 +11160,7 @@
       <c r="X6" s="6"/>
       <c r="Y6" s="6"/>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25">
       <c r="A7" s="8">
         <v>45992</v>
       </c>
@@ -11062,7 +11219,7 @@
       <c r="X7" s="6"/>
       <c r="Y7" s="6"/>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25">
       <c r="A8" s="8">
         <v>45999</v>
       </c>
@@ -11121,7 +11278,7 @@
       <c r="X8" s="6"/>
       <c r="Y8" s="6"/>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25">
       <c r="A9" s="8">
         <v>46006</v>
       </c>
@@ -11180,7 +11337,7 @@
       <c r="X9" s="6"/>
       <c r="Y9" s="6"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25">
       <c r="A10" s="8">
         <v>46013</v>
       </c>
@@ -11239,7 +11396,7 @@
       <c r="X10" s="6"/>
       <c r="Y10" s="6"/>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25">
       <c r="A11" s="8">
         <v>46020</v>
       </c>
@@ -11298,7 +11455,7 @@
       <c r="X11" s="6"/>
       <c r="Y11" s="6"/>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25">
       <c r="A12" s="8">
         <v>46027</v>
       </c>
@@ -11357,7 +11514,7 @@
       <c r="X12" s="6"/>
       <c r="Y12" s="6"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25">
       <c r="A13" s="8">
         <v>46034</v>
       </c>
@@ -11416,7 +11573,7 @@
       <c r="X13" s="6"/>
       <c r="Y13" s="6"/>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25">
       <c r="A14" s="8">
         <v>46041</v>
       </c>
@@ -11475,7 +11632,7 @@
       <c r="X14" s="6"/>
       <c r="Y14" s="6"/>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25">
       <c r="A15" s="8">
         <v>46048</v>
       </c>
@@ -11534,7 +11691,7 @@
       <c r="X15" s="6"/>
       <c r="Y15" s="6"/>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25">
       <c r="A16" s="8">
         <v>46055</v>
       </c>
@@ -11584,7 +11741,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16">
       <c r="A17" s="8">
         <v>46062</v>
       </c>
@@ -11634,7 +11791,7 @@
         <v>12.95</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16">
       <c r="A18" s="8">
         <v>46076</v>
       </c>
@@ -11684,7 +11841,7 @@
         <v>13.05</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16">
       <c r="A19" s="8">
         <v>46083</v>
       </c>
@@ -11734,7 +11891,7 @@
         <v>13.05</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16">
       <c r="A20" s="8">
         <v>46090</v>
       </c>
@@ -11784,7 +11941,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16">
       <c r="A21" s="8">
         <v>46097</v>
       </c>
@@ -11834,7 +11991,7 @@
         <v>17.95</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16">
       <c r="A22" s="8">
         <v>46104</v>
       </c>
@@ -11884,7 +12041,7 @@
         <v>18.95</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16">
       <c r="A23" s="8">
         <v>46111</v>
       </c>
@@ -11934,7 +12091,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16">
       <c r="A24" s="8">
         <v>46118</v>
       </c>
@@ -11984,7 +12141,7 @@
         <v>18.55</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16">
       <c r="A25" s="8">
         <v>46125</v>
       </c>
@@ -12034,7 +12191,7 @@
         <v>18.25</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16">
       <c r="A26" s="8">
         <v>46132</v>
       </c>
@@ -12084,7 +12241,7 @@
         <v>17.55</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16">
       <c r="A27" s="8">
         <v>46139</v>
       </c>
@@ -12134,7 +12291,7 @@
         <v>16.649999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16">
       <c r="A28" s="8">
         <v>46146</v>
       </c>
@@ -12184,7 +12341,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16">
       <c r="A29" s="8">
         <v>46153</v>
       </c>
@@ -12234,7 +12391,7 @@
         <v>15.85</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16">
       <c r="A30" s="8">
         <v>46160</v>
       </c>
@@ -12284,7 +12441,7 @@
         <v>15.35</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16">
       <c r="A31" s="8">
         <v>46167</v>
       </c>
@@ -12334,7 +12491,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16">
       <c r="A32" s="8">
         <v>46174</v>
       </c>
@@ -12384,7 +12541,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16">
       <c r="A33" s="8">
         <v>46181</v>
       </c>
@@ -12434,7 +12591,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16">
       <c r="A34" s="8">
         <v>46188</v>
       </c>
@@ -12484,7 +12641,7 @@
         <v>13.55</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16">
       <c r="A35" s="8">
         <v>46195</v>
       </c>
@@ -12534,7 +12691,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16">
       <c r="A36" s="8">
         <v>46202</v>
       </c>
@@ -12584,7 +12741,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16">
       <c r="A37" s="8">
         <v>46209</v>
       </c>
@@ -12634,7 +12791,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16">
       <c r="A38" s="8">
         <v>46216</v>
       </c>
@@ -12684,7 +12841,7 @@
         <v>12.625</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16">
       <c r="A39" s="8">
         <v>46223</v>
       </c>
@@ -12734,7 +12891,7 @@
         <v>12.55</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16">
       <c r="A40" s="8">
         <v>46230</v>
       </c>
@@ -12784,7 +12941,7 @@
         <v>12.45</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16">
       <c r="A41" s="8">
         <v>46237</v>
       </c>
@@ -12832,6 +12989,56 @@
       </c>
       <c r="P41" s="11">
         <v>12.45</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42" s="8">
+        <v>46244</v>
+      </c>
+      <c r="B42" s="8">
+        <v>46251</v>
+      </c>
+      <c r="C42" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E42" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="F42" s="11">
+        <v>2.85</v>
+      </c>
+      <c r="G42" s="11">
+        <v>2.9649999999999999</v>
+      </c>
+      <c r="H42" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="I42" s="11">
+        <v>4</v>
+      </c>
+      <c r="J42" s="11">
+        <v>4.375</v>
+      </c>
+      <c r="K42" s="11">
+        <v>7.1</v>
+      </c>
+      <c r="L42" s="11">
+        <v>6.2</v>
+      </c>
+      <c r="M42" s="11">
+        <v>6.65</v>
+      </c>
+      <c r="N42" s="11">
+        <v>13</v>
+      </c>
+      <c r="O42" s="11">
+        <v>12</v>
+      </c>
+      <c r="P42" s="11">
+        <v>12.425000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -12849,19 +13056,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD3DFE18-E6A7-46E2-A20D-CA2E453C377B}">
   <dimension ref="A1:Y5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="11.3984375" style="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.3984375" style="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="13.19921875" style="22" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.19921875" style="22" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="13.1640625" style="22" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.1640625" style="22" bestFit="1" customWidth="1"/>
     <col min="17" max="25" width="9" style="22"/>
     <col min="26" max="16384" width="9" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="16" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" s="16" customFormat="1">
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
@@ -12914,7 +13121,7 @@
       <c r="X1" s="15"/>
       <c r="Y1" s="15"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25">
       <c r="A2" s="26"/>
       <c r="B2" s="26"/>
       <c r="C2" s="27"/>
@@ -12959,7 +13166,7 @@
       <c r="X2" s="17"/>
       <c r="Y2" s="17"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25">
       <c r="A3" s="19">
         <v>45930</v>
       </c>
@@ -13012,7 +13219,7 @@
       <c r="X3" s="17"/>
       <c r="Y3" s="17"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25">
       <c r="A4" s="19">
         <v>46042</v>
       </c>
@@ -13065,7 +13272,7 @@
       <c r="X4" s="17"/>
       <c r="Y4" s="17"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25">
       <c r="A5" s="19">
         <v>46139</v>
       </c>
@@ -13120,22 +13327,22 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A9E7BC-4FDA-42FF-94EB-B5FEB168C665}">
-  <dimension ref="A1:AJ21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AJ22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.3984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="22" width="10.3984375" style="11" customWidth="1"/>
-    <col min="23" max="24" width="7.796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.3984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="26" max="28" width="10.59765625" style="11" customWidth="1"/>
+    <col min="5" max="22" width="10.33203125" style="11" customWidth="1"/>
+    <col min="23" max="24" width="7.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="10.6640625" style="11" customWidth="1"/>
     <col min="29" max="36" width="9" style="11"/>
     <col min="37" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" s="5" customFormat="1">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -13229,7 +13436,7 @@
       <c r="AI1" s="4"/>
       <c r="AJ1" s="4"/>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36">
       <c r="A2" s="23"/>
       <c r="B2" s="23"/>
       <c r="C2" s="24"/>
@@ -13315,7 +13522,7 @@
       <c r="AI2" s="6"/>
       <c r="AJ2" s="6"/>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36">
       <c r="A3" s="12">
         <v>45961</v>
       </c>
@@ -13391,7 +13598,7 @@
       <c r="AI3" s="6"/>
       <c r="AJ3" s="6"/>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36">
       <c r="A4" s="12">
         <v>45975</v>
       </c>
@@ -13467,7 +13674,7 @@
       <c r="AI4" s="6"/>
       <c r="AJ4" s="6"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36">
       <c r="A5" s="12">
         <v>45989</v>
       </c>
@@ -13543,7 +13750,7 @@
       <c r="AI5" s="6"/>
       <c r="AJ5" s="6"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36">
       <c r="A6" s="12">
         <v>46003</v>
       </c>
@@ -13619,7 +13826,7 @@
       <c r="AI6" s="6"/>
       <c r="AJ6" s="6"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36">
       <c r="A7" s="12">
         <v>46017</v>
       </c>
@@ -13689,7 +13896,7 @@
       <c r="AI7" s="6"/>
       <c r="AJ7" s="6"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36">
       <c r="A8" s="8">
         <v>46034</v>
       </c>
@@ -13765,7 +13972,7 @@
       <c r="AI8" s="6"/>
       <c r="AJ8" s="6"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36">
       <c r="A9" s="8">
         <v>46052</v>
       </c>
@@ -13841,7 +14048,7 @@
       <c r="AI9" s="6"/>
       <c r="AJ9" s="6"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36">
       <c r="A10" s="8">
         <v>46066</v>
       </c>
@@ -13900,7 +14107,7 @@
         <v>155.79</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36">
       <c r="A11" s="8">
         <v>46079</v>
       </c>
@@ -13959,7 +14166,7 @@
         <v>167.79</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36">
       <c r="A12" s="8">
         <v>46097</v>
       </c>
@@ -14018,7 +14225,7 @@
         <v>155.88</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36">
       <c r="A13" s="8">
         <v>46108</v>
       </c>
@@ -14077,7 +14284,7 @@
         <v>135.97</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36">
       <c r="A14" s="8">
         <v>46129</v>
       </c>
@@ -14136,7 +14343,7 @@
         <v>154.97</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36">
       <c r="A15" s="8">
         <v>46142</v>
       </c>
@@ -14195,7 +14402,7 @@
         <v>158.88</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36">
       <c r="A16" s="8">
         <v>46157</v>
       </c>
@@ -14254,7 +14461,7 @@
         <v>176.97</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22">
       <c r="A17" s="8">
         <v>46171</v>
       </c>
@@ -14313,7 +14520,7 @@
         <v>174.79</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:22">
       <c r="A18" s="8">
         <v>46185</v>
       </c>
@@ -14372,7 +14579,7 @@
         <v>167.97</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:22">
       <c r="A19" s="8">
         <v>46199</v>
       </c>
@@ -14431,7 +14638,7 @@
         <v>164.97</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:22">
       <c r="A20" s="8">
         <v>46220</v>
       </c>
@@ -14490,7 +14697,7 @@
         <v>165.97</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:22">
       <c r="A21" s="8">
         <v>46234</v>
       </c>
@@ -14546,6 +14753,65 @@
         <v>164.97</v>
       </c>
       <c r="V21" s="11">
+        <v>164.97</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
+      <c r="A22" s="8">
+        <v>46248</v>
+      </c>
+      <c r="B22" s="8">
+        <v>46248</v>
+      </c>
+      <c r="C22" s="9">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" s="11">
+        <v>178.67</v>
+      </c>
+      <c r="F22" s="11">
+        <v>178.67</v>
+      </c>
+      <c r="G22" s="11">
+        <v>178.67</v>
+      </c>
+      <c r="H22" s="11">
+        <v>150.30000000000001</v>
+      </c>
+      <c r="I22" s="11">
+        <v>115.7</v>
+      </c>
+      <c r="J22" s="11">
+        <v>133</v>
+      </c>
+      <c r="K22" s="11">
+        <v>239.99</v>
+      </c>
+      <c r="L22" s="11">
+        <v>238.88</v>
+      </c>
+      <c r="M22" s="11">
+        <v>239.44</v>
+      </c>
+      <c r="Q22" s="11">
+        <v>390</v>
+      </c>
+      <c r="R22" s="11">
+        <v>390</v>
+      </c>
+      <c r="S22" s="11">
+        <v>390</v>
+      </c>
+      <c r="T22" s="11">
+        <v>164.97</v>
+      </c>
+      <c r="U22" s="11">
+        <v>164.97</v>
+      </c>
+      <c r="V22" s="11">
         <v>164.97</v>
       </c>
     </row>
@@ -14564,7 +14830,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{303223D0-B4CB-49AA-99CE-D17D229E45B9}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14576,14 +14842,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF9DD02-7584-4E7B-8430-E8812C31F69E}">
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3">
       <c r="B1" s="2" t="s">
         <v>61</v>
       </c>
@@ -14591,7 +14857,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -14602,7 +14868,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3">
       <c r="A3" s="2"/>
       <c r="B3" s="1" t="s">
         <v>11</v>
@@ -14611,7 +14877,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3">
       <c r="A4" s="2"/>
       <c r="B4" s="1" t="s">
         <v>12</v>
@@ -14620,7 +14886,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3">
       <c r="A5" s="2"/>
       <c r="B5" s="1" t="s">
         <v>14</v>
@@ -14629,7 +14895,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
@@ -14638,21 +14904,21 @@
       </c>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3">
       <c r="A7" s="2"/>
       <c r="B7" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3">
       <c r="A8" s="2"/>
       <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
@@ -14663,7 +14929,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3">
       <c r="A10" s="2"/>
       <c r="B10" s="1" t="s">
         <v>23</v>
@@ -14672,7 +14938,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3">
       <c r="A11" s="2"/>
       <c r="B11" s="1" t="s">
         <v>24</v>
@@ -14681,7 +14947,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
         <v>25</v>
       </c>
@@ -14690,28 +14956,28 @@
       </c>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3">
       <c r="A13" s="2"/>
       <c r="B13" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3">
       <c r="A14" s="2"/>
       <c r="B14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3">
       <c r="A15" s="2"/>
       <c r="B15" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
         <v>30</v>
       </c>
@@ -14720,21 +14986,21 @@
       </c>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3">
       <c r="A17" s="2"/>
       <c r="B17" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3">
       <c r="A18" s="2"/>
       <c r="B18" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
         <v>34</v>
       </c>
@@ -14745,7 +15011,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3">
       <c r="A20" s="2"/>
       <c r="B20" s="1" t="s">
         <v>37</v>
@@ -14754,7 +15020,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3">
       <c r="A21" s="2"/>
       <c r="B21" s="1" t="s">
         <v>35</v>
@@ -14763,7 +15029,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3">
       <c r="A22" s="2"/>
       <c r="B22" s="1" t="s">
         <v>35</v>
@@ -14772,7 +15038,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3">
       <c r="A23" s="2"/>
       <c r="B23" s="1" t="s">
         <v>35</v>
@@ -14781,7 +15047,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
         <v>42</v>
       </c>
@@ -14790,28 +15056,28 @@
       </c>
       <c r="C24" s="1"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3">
       <c r="A25" s="2"/>
       <c r="B25" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C25" s="1"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3">
       <c r="A26" s="2"/>
       <c r="B26" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C26" s="1"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3">
       <c r="A27" s="2"/>
       <c r="B27" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C27" s="1"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3">
       <c r="A28" s="2" t="s">
         <v>47</v>
       </c>
@@ -14820,42 +15086,42 @@
       </c>
       <c r="C28" s="1"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3">
       <c r="A29" s="2"/>
       <c r="B29" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C29" s="1"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3">
       <c r="A30" s="2"/>
       <c r="B30" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C30" s="1"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:3">
       <c r="A31" s="2"/>
       <c r="B31" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C31" s="1"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:3">
       <c r="A32" s="2"/>
       <c r="B32" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C32" s="1"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:3">
       <c r="A33" s="2"/>
       <c r="B33" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C33" s="1"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
         <v>54</v>
       </c>
@@ -14864,35 +15130,35 @@
       </c>
       <c r="C34" s="1"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:3">
       <c r="A35" s="2"/>
       <c r="B35" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C35" s="1"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:3">
       <c r="A36" s="2"/>
       <c r="B36" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C36" s="1"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:3">
       <c r="A37" s="2"/>
       <c r="B37" s="1" t="s">
         <v>58</v>
       </c>
       <c r="C37" s="1"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:3">
       <c r="A38" s="2"/>
       <c r="B38" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C38" s="1"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:3">
       <c r="A39" s="2"/>
       <c r="B39" s="1" t="s">
         <v>60</v>

--- a/data_lake/industry/TrendForce/NAND Flash.xlsx
+++ b/data_lake/industry/TrendForce/NAND Flash.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/industry/TrendForce/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D6E458-31F2-2A4E-B3B3-D3E008130673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7615FE5F-2632-2A47-B457-A2F0E7ACD2AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25640" yWindow="600" windowWidth="25560" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17280" yWindow="780" windowWidth="18720" windowHeight="20700" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="fig" sheetId="8" r:id="rId7"/>
     <sheet name="info" sheetId="2" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="76">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -635,6 +635,9 @@
                 <c:pt idx="29">
                   <c:v>46251</c:v>
                 </c:pt>
+                <c:pt idx="30">
+                  <c:v>46258</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -733,6 +736,9 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>4.3</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>4.2830000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -869,6 +875,9 @@
                 <c:pt idx="29">
                   <c:v>46251</c:v>
                 </c:pt>
+                <c:pt idx="30">
+                  <c:v>46258</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -967,6 +976,9 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>3.4950000000000001</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3.48</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1103,6 +1115,9 @@
                 <c:pt idx="29">
                   <c:v>46251</c:v>
                 </c:pt>
+                <c:pt idx="30">
+                  <c:v>46258</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1201,6 +1216,9 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>35.75</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>36.587000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1337,6 +1355,9 @@
                 <c:pt idx="29">
                   <c:v>46251</c:v>
                 </c:pt>
+                <c:pt idx="30">
+                  <c:v>46258</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1435,6 +1456,9 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>17.437999999999999</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>17.937999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1823,6 +1847,9 @@
                 <c:pt idx="39">
                   <c:v>46251</c:v>
                 </c:pt>
+                <c:pt idx="40">
+                  <c:v>46258</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1951,6 +1978,9 @@
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>21.125</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>21.207999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2117,6 +2147,9 @@
                 <c:pt idx="39">
                   <c:v>46251</c:v>
                 </c:pt>
+                <c:pt idx="40">
+                  <c:v>46258</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2245,6 +2278,9 @@
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>14.731</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>15.923</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2411,6 +2447,9 @@
                 <c:pt idx="39">
                   <c:v>46251</c:v>
                 </c:pt>
+                <c:pt idx="40">
+                  <c:v>46258</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2539,6 +2578,9 @@
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>9.6329999999999991</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2927,6 +2969,9 @@
                 <c:pt idx="39">
                   <c:v>46251</c:v>
                 </c:pt>
+                <c:pt idx="40">
+                  <c:v>46258</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3054,6 +3099,9 @@
                   <c:v>2.9649999999999999</c:v>
                 </c:pt>
                 <c:pt idx="39">
+                  <c:v>2.9649999999999999</c:v>
+                </c:pt>
+                <c:pt idx="40">
                   <c:v>2.9649999999999999</c:v>
                 </c:pt>
               </c:numCache>
@@ -3221,6 +3269,9 @@
                 <c:pt idx="39">
                   <c:v>46251</c:v>
                 </c:pt>
+                <c:pt idx="40">
+                  <c:v>46258</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3349,6 +3400,9 @@
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>4.375</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>4.3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3515,6 +3569,9 @@
                 <c:pt idx="39">
                   <c:v>46251</c:v>
                 </c:pt>
+                <c:pt idx="40">
+                  <c:v>46258</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3643,6 +3700,9 @@
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>6.65</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>6.55</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3809,6 +3869,9 @@
                 <c:pt idx="39">
                   <c:v>46251</c:v>
                 </c:pt>
+                <c:pt idx="40">
+                  <c:v>46258</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3937,6 +4000,9 @@
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>12.425000000000001</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>12.35</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6201,7 +6267,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y42"/>
+  <dimension ref="A1:Y43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
@@ -8437,6 +8503,56 @@
       </c>
       <c r="P42" s="11">
         <v>17.437999999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43" s="8">
+        <v>46251</v>
+      </c>
+      <c r="B43" s="8">
+        <v>46258</v>
+      </c>
+      <c r="C43" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E43" s="11">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="F43" s="11">
+        <v>4</v>
+      </c>
+      <c r="G43" s="11">
+        <v>4.2830000000000004</v>
+      </c>
+      <c r="H43" s="11">
+        <v>3.75</v>
+      </c>
+      <c r="I43" s="11">
+        <v>3.13</v>
+      </c>
+      <c r="J43" s="11">
+        <v>3.48</v>
+      </c>
+      <c r="K43" s="11">
+        <v>55</v>
+      </c>
+      <c r="L43" s="11">
+        <v>32</v>
+      </c>
+      <c r="M43" s="11">
+        <v>36.587000000000003</v>
+      </c>
+      <c r="N43" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="O43" s="11">
+        <v>17</v>
+      </c>
+      <c r="P43" s="11">
+        <v>17.937999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -8882,7 +8998,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54319F21-0FC0-45E2-9E0C-131772CB34B0}">
-  <dimension ref="A1:Y42"/>
+  <dimension ref="A1:Y43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
@@ -10785,6 +10901,47 @@
       </c>
       <c r="M42" s="11">
         <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
+      <c r="A43" s="8">
+        <v>46251</v>
+      </c>
+      <c r="B43" s="8">
+        <v>46258</v>
+      </c>
+      <c r="C43" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E43" s="11">
+        <v>23</v>
+      </c>
+      <c r="F43" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="G43" s="11">
+        <v>21.207999999999998</v>
+      </c>
+      <c r="H43" s="11">
+        <v>19</v>
+      </c>
+      <c r="I43" s="11">
+        <v>14</v>
+      </c>
+      <c r="J43" s="11">
+        <v>15.923</v>
+      </c>
+      <c r="K43" s="11">
+        <v>15</v>
+      </c>
+      <c r="L43" s="11">
+        <v>8</v>
+      </c>
+      <c r="M43" s="11">
+        <v>9.6329999999999991</v>
       </c>
     </row>
   </sheetData>
@@ -10801,7 +10958,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B53F4-91AF-4D49-84B3-FC7BC3C51C10}">
-  <dimension ref="A1:Y42"/>
+  <dimension ref="A1:Y43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
@@ -13039,6 +13196,56 @@
       </c>
       <c r="P42" s="11">
         <v>12.425000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43" s="8">
+        <v>46251</v>
+      </c>
+      <c r="B43" s="8">
+        <v>46258</v>
+      </c>
+      <c r="C43" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E43" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="F43" s="11">
+        <v>2.85</v>
+      </c>
+      <c r="G43" s="11">
+        <v>2.9649999999999999</v>
+      </c>
+      <c r="H43" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="I43" s="11">
+        <v>3.9</v>
+      </c>
+      <c r="J43" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="K43" s="11">
+        <v>7</v>
+      </c>
+      <c r="L43" s="11">
+        <v>6</v>
+      </c>
+      <c r="M43" s="11">
+        <v>6.55</v>
+      </c>
+      <c r="N43" s="11">
+        <v>13</v>
+      </c>
+      <c r="O43" s="11">
+        <v>12</v>
+      </c>
+      <c r="P43" s="11">
+        <v>12.35</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/industry/TrendForce/NAND Flash.xlsx
+++ b/data_lake/industry/TrendForce/NAND Flash.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7615FE5F-2632-2A47-B457-A2F0E7ACD2AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0609B3B-4093-004C-877C-252A7DA6EFD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17280" yWindow="780" windowWidth="18720" windowHeight="20700" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17280" yWindow="780" windowWidth="18720" windowHeight="20700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="76">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -638,6 +638,9 @@
                 <c:pt idx="30">
                   <c:v>46258</c:v>
                 </c:pt>
+                <c:pt idx="31">
+                  <c:v>46265</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -739,6 +742,9 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>4.2830000000000004</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>4.2850000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -878,6 +884,9 @@
                 <c:pt idx="30">
                   <c:v>46258</c:v>
                 </c:pt>
+                <c:pt idx="31">
+                  <c:v>46265</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -979,6 +988,9 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>3.48</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>3.4449999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1118,6 +1130,9 @@
                 <c:pt idx="30">
                   <c:v>46258</c:v>
                 </c:pt>
+                <c:pt idx="31">
+                  <c:v>46265</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1219,6 +1234,9 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>36.587000000000003</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>37.587000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1358,6 +1376,9 @@
                 <c:pt idx="30">
                   <c:v>46258</c:v>
                 </c:pt>
+                <c:pt idx="31">
+                  <c:v>46265</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1459,6 +1480,9 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>17.937999999999999</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>18.437999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1850,6 +1874,9 @@
                 <c:pt idx="40">
                   <c:v>46258</c:v>
                 </c:pt>
+                <c:pt idx="41">
+                  <c:v>46265</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1981,6 +2008,9 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>21.207999999999998</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>20.896000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2150,6 +2180,9 @@
                 <c:pt idx="40">
                   <c:v>46258</c:v>
                 </c:pt>
+                <c:pt idx="41">
+                  <c:v>46265</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2281,6 +2314,9 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>15.923</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>16.808</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2450,6 +2486,9 @@
                 <c:pt idx="40">
                   <c:v>46258</c:v>
                 </c:pt>
+                <c:pt idx="41">
+                  <c:v>46265</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2581,6 +2620,9 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>9.6329999999999991</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>9.9670000000000005</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2972,6 +3014,9 @@
                 <c:pt idx="40">
                   <c:v>46258</c:v>
                 </c:pt>
+                <c:pt idx="41">
+                  <c:v>46265</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3102,6 +3147,9 @@
                   <c:v>2.9649999999999999</c:v>
                 </c:pt>
                 <c:pt idx="40">
+                  <c:v>2.9649999999999999</c:v>
+                </c:pt>
+                <c:pt idx="41">
                   <c:v>2.9649999999999999</c:v>
                 </c:pt>
               </c:numCache>
@@ -3272,6 +3320,9 @@
                 <c:pt idx="40">
                   <c:v>46258</c:v>
                 </c:pt>
+                <c:pt idx="41">
+                  <c:v>46265</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3403,6 +3454,9 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>4.3</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>4.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3572,6 +3626,9 @@
                 <c:pt idx="40">
                   <c:v>46258</c:v>
                 </c:pt>
+                <c:pt idx="41">
+                  <c:v>46265</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3703,6 +3760,9 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>6.55</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>6.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3872,6 +3932,9 @@
                 <c:pt idx="40">
                   <c:v>46258</c:v>
                 </c:pt>
+                <c:pt idx="41">
+                  <c:v>46265</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4003,6 +4066,9 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>12.35</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>12.3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6267,7 +6333,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y43"/>
+  <dimension ref="A1:Y44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
@@ -8553,6 +8619,56 @@
       </c>
       <c r="P43" s="11">
         <v>17.937999999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44" s="8">
+        <v>46258</v>
+      </c>
+      <c r="B44" s="8">
+        <v>46265</v>
+      </c>
+      <c r="C44" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E44" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F44" s="11">
+        <v>4.08</v>
+      </c>
+      <c r="G44" s="11">
+        <v>4.2850000000000001</v>
+      </c>
+      <c r="H44" s="11">
+        <v>3.7</v>
+      </c>
+      <c r="I44" s="11">
+        <v>3</v>
+      </c>
+      <c r="J44" s="11">
+        <v>3.4449999999999998</v>
+      </c>
+      <c r="K44" s="11">
+        <v>55</v>
+      </c>
+      <c r="L44" s="11">
+        <v>33</v>
+      </c>
+      <c r="M44" s="11">
+        <v>37.587000000000003</v>
+      </c>
+      <c r="N44" s="11">
+        <v>20</v>
+      </c>
+      <c r="O44" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="P44" s="11">
+        <v>18.437999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -8570,12 +8686,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A6DA72B-EEC5-42C3-B327-5A9F9ACABB0A}">
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.33203125" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
@@ -8982,6 +9098,47 @@
       </c>
       <c r="M9" s="11">
         <v>17.074999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
+      <c r="A10" s="8">
+        <v>46234</v>
+      </c>
+      <c r="B10" s="8">
+        <v>46265</v>
+      </c>
+      <c r="C10" s="9">
+        <v>0.375</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="11">
+        <v>30.2</v>
+      </c>
+      <c r="F10" s="11">
+        <v>29.6</v>
+      </c>
+      <c r="G10" s="11">
+        <v>30.047999999999998</v>
+      </c>
+      <c r="H10" s="11">
+        <v>23.3</v>
+      </c>
+      <c r="I10" s="11">
+        <v>22.8</v>
+      </c>
+      <c r="J10" s="11">
+        <v>23.11</v>
+      </c>
+      <c r="K10" s="11">
+        <v>18.2</v>
+      </c>
+      <c r="L10" s="11">
+        <v>17.55</v>
+      </c>
+      <c r="M10" s="11">
+        <v>17.864999999999998</v>
       </c>
     </row>
   </sheetData>
@@ -8998,7 +9155,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54319F21-0FC0-45E2-9E0C-131772CB34B0}">
-  <dimension ref="A1:Y43"/>
+  <dimension ref="A1:Y44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
@@ -10942,6 +11099,47 @@
       </c>
       <c r="M43" s="11">
         <v>9.6329999999999991</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
+      <c r="A44" s="8">
+        <v>46258</v>
+      </c>
+      <c r="B44" s="8">
+        <v>46265</v>
+      </c>
+      <c r="C44" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E44" s="11">
+        <v>22.5</v>
+      </c>
+      <c r="F44" s="11">
+        <v>17</v>
+      </c>
+      <c r="G44" s="11">
+        <v>20.896000000000001</v>
+      </c>
+      <c r="H44" s="11">
+        <v>19</v>
+      </c>
+      <c r="I44" s="11">
+        <v>14</v>
+      </c>
+      <c r="J44" s="11">
+        <v>16.808</v>
+      </c>
+      <c r="K44" s="11">
+        <v>15</v>
+      </c>
+      <c r="L44" s="11">
+        <v>8</v>
+      </c>
+      <c r="M44" s="11">
+        <v>9.9670000000000005</v>
       </c>
     </row>
   </sheetData>
@@ -10958,7 +11156,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B53F4-91AF-4D49-84B3-FC7BC3C51C10}">
-  <dimension ref="A1:Y43"/>
+  <dimension ref="A1:Y44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
@@ -13246,6 +13444,56 @@
       </c>
       <c r="P43" s="11">
         <v>12.35</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44" s="8">
+        <v>46258</v>
+      </c>
+      <c r="B44" s="8">
+        <v>46265</v>
+      </c>
+      <c r="C44" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E44" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="F44" s="11">
+        <v>2.85</v>
+      </c>
+      <c r="G44" s="11">
+        <v>2.9649999999999999</v>
+      </c>
+      <c r="H44" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="I44" s="11">
+        <v>3.9</v>
+      </c>
+      <c r="J44" s="11">
+        <v>4.25</v>
+      </c>
+      <c r="K44" s="11">
+        <v>7</v>
+      </c>
+      <c r="L44" s="11">
+        <v>6</v>
+      </c>
+      <c r="M44" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="N44" s="11">
+        <v>13</v>
+      </c>
+      <c r="O44" s="11">
+        <v>12</v>
+      </c>
+      <c r="P44" s="11">
+        <v>12.3</v>
       </c>
     </row>
   </sheetData>
@@ -13534,7 +13782,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A9E7BC-4FDA-42FF-94EB-B5FEB168C665}">
-  <dimension ref="A1:AJ22"/>
+  <dimension ref="A1:AJ23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="8" bestFit="1" customWidth="1"/>
@@ -15020,6 +15268,65 @@
       </c>
       <c r="V22" s="11">
         <v>164.97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
+      <c r="A23" s="8">
+        <v>46262</v>
+      </c>
+      <c r="B23" s="8">
+        <v>46262</v>
+      </c>
+      <c r="C23" s="9">
+        <v>0.4375</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E23" s="11">
+        <v>181.88</v>
+      </c>
+      <c r="F23" s="11">
+        <v>178.67</v>
+      </c>
+      <c r="G23" s="11">
+        <v>180.28</v>
+      </c>
+      <c r="H23" s="11">
+        <v>150.30000000000001</v>
+      </c>
+      <c r="I23" s="11">
+        <v>115.7</v>
+      </c>
+      <c r="J23" s="11">
+        <v>133</v>
+      </c>
+      <c r="K23" s="11">
+        <v>239.99</v>
+      </c>
+      <c r="L23" s="11">
+        <v>239.99</v>
+      </c>
+      <c r="M23" s="11">
+        <v>239.99</v>
+      </c>
+      <c r="Q23" s="11">
+        <v>390</v>
+      </c>
+      <c r="R23" s="11">
+        <v>390</v>
+      </c>
+      <c r="S23" s="11">
+        <v>390</v>
+      </c>
+      <c r="T23" s="11">
+        <v>189.97</v>
+      </c>
+      <c r="U23" s="11">
+        <v>164.97</v>
+      </c>
+      <c r="V23" s="11">
+        <v>177.47</v>
       </c>
     </row>
   </sheetData>
